--- a/app/src/documents/__fixtures__/golden/Contest Day Schedule.xlsx
+++ b/app/src/documents/__fixtures__/golden/Contest Day Schedule.xlsx
@@ -172,6 +172,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDADADA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDADADA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEF2CB"/>
         <bgColor/>
       </patternFill>
@@ -239,18 +251,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDADADA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDADADA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -710,212 +710,212 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>0.4166666666666667</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>0.4513888888888889</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="10" t="str">
         <v>Bravo HS — Setup and Performance</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="10" t="str">
         <v>The Crucible</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>0.4513888888888889</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>0.4618055555555556</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="10" t="str">
         <v>School 1 Strike — School 2 Setup</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="10" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="11">
         <v>0.4618055555555556</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="11">
         <v>0.4895833333333333</v>
       </c>
-      <c r="C8" s="10" t="str">
+      <c r="C8" s="12" t="str">
         <v>Delta HS — Performance</v>
       </c>
-      <c r="D8" s="10" t="str">
+      <c r="D8" s="12" t="str">
         <v>Metamorphoses</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <v>0.4895833333333333</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="11">
         <v>0.5</v>
       </c>
-      <c r="C9" s="10" t="str">
+      <c r="C9" s="12" t="str">
         <v>School 2 Strike — School 3 Setup</v>
       </c>
-      <c r="D9" s="10" t="str">
+      <c r="D9" s="12" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11">
+      <c r="A10" s="13">
         <v>0.5</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="13">
         <v>0.5277777777777778</v>
       </c>
-      <c r="C10" s="12" t="str">
+      <c r="C10" s="14" t="str">
         <v>Alpha HS — Performance</v>
       </c>
-      <c r="D10" s="12" t="str">
+      <c r="D10" s="14" t="str">
         <v>Romeo &amp; Juliet</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11">
+      <c r="A11" s="13">
         <v>0.5277777777777778</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="13">
         <v>0.5381944444444444</v>
       </c>
-      <c r="C11" s="12" t="str">
+      <c r="C11" s="14" t="str">
         <v>School 3 Strike — School 4 Setup</v>
       </c>
-      <c r="D11" s="12" t="str">
+      <c r="D11" s="14" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="15">
         <v>0.5381944444444444</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="15">
         <v>0.5659722222222222</v>
       </c>
-      <c r="C12" s="14" t="str">
+      <c r="C12" s="16" t="str">
         <v>Foxtrot HS — Performance</v>
       </c>
-      <c r="D12" s="14" t="str">
+      <c r="D12" s="16" t="str">
         <v>Radium Girls</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="15">
         <v>0.5659722222222222</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="15">
         <v>0.5763888888888888</v>
       </c>
-      <c r="C13" s="14" t="str">
+      <c r="C13" s="16" t="str">
         <v>School 4 Strike — School 5 Setup</v>
       </c>
-      <c r="D13" s="14" t="str">
+      <c r="D13" s="16" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>0.5763888888888888</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="17">
         <v>0.6041666666666666</v>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C14" s="18" t="str">
         <v>Charlie HS — Performance</v>
       </c>
-      <c r="D14" s="16" t="str">
+      <c r="D14" s="18" t="str">
         <v>Antigone</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15">
+      <c r="A15" s="17">
         <v>0.6041666666666666</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="17">
         <v>0.6145833333333334</v>
       </c>
-      <c r="C15" s="16" t="str">
+      <c r="C15" s="18" t="str">
         <v>School 5 Strike — School 6 Setup</v>
       </c>
-      <c r="D15" s="16" t="str">
+      <c r="D15" s="18" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17">
+      <c r="A16" s="19">
         <v>0.6145833333333334</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="19">
         <v>0.6423611111111112</v>
       </c>
-      <c r="C16" s="18" t="str">
+      <c r="C16" s="20" t="str">
         <v>Echo HS — Performance</v>
       </c>
-      <c r="D16" s="18" t="str">
+      <c r="D16" s="20" t="str">
         <v>Almost, Maine</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17">
+      <c r="A17" s="19">
         <v>0.6423611111111112</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="19">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C17" s="18" t="str">
+      <c r="C17" s="20" t="str">
         <v>School 6 Strike</v>
       </c>
-      <c r="D17" s="18" t="str">
+      <c r="D17" s="20" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19">
+      <c r="A18" s="7">
         <v>0.6527777777777778</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="7">
         <v>0.6736111111111112</v>
       </c>
-      <c r="C18" s="20" t="str">
+      <c r="C18" s="8" t="str">
         <v>Judge's Tabulation</v>
       </c>
-      <c r="D18" s="20" t="str">
+      <c r="D18" s="8" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19">
+      <c r="A19" s="7">
         <v>0.6736111111111112</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="7">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C19" s="20" t="str">
+      <c r="C19" s="8" t="str">
         <v>Critiques — 3 Judges Concurrent</v>
       </c>
-      <c r="D19" s="20" t="str">
+      <c r="D19" s="8" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19">
+      <c r="A20" s="7">
         <v>0.6944444444444444</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="7">
         <v>0.7152777777777778</v>
       </c>
-      <c r="C20" s="20" t="str">
+      <c r="C20" s="8" t="str">
         <v>Awards Ceremony</v>
       </c>
-      <c r="D20" s="20" t="str">
+      <c r="D20" s="8" t="str">
         <v/>
       </c>
     </row>
